--- a/dataland-framework-toolbox/inputs/eu-taxonomy-financials/eu-taxonomy-financials.xlsx
+++ b/dataland-framework-toolbox/inputs/eu-taxonomy-financials/eu-taxonomy-financials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\eu-taxonomy-financials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084878DE-4FFF-48F7-8057-9BD152E7B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9E55F9-2C90-483D-87E8-3D1418C0EA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="708">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -2177,9 +2177,6 @@
   </si>
   <si>
     <t>Does Article 1(2) of Regulation (EU) 2020/852 apply to the undertaking and, therefore, is EU Taxonomy data reported on a mandatory basis?</t>
-  </si>
-  <si>
-    <t>Identity: [extendedEnumYesNoIsNfrdMandatory]</t>
   </si>
 </sst>
 </file>
@@ -2969,7 +2966,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3385,12 +3382,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3945,7 +3936,7 @@
       <c r="E7" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="143" t="s">
+      <c r="F7" s="142" t="s">
         <v>707</v>
       </c>
       <c r="G7" s="18" t="s">
@@ -3964,9 +3955,7 @@
       <c r="P7" s="16" t="s">
         <v>705</v>
       </c>
-      <c r="Q7" s="144" t="s">
-        <v>708</v>
-      </c>
+      <c r="Q7" s="142"/>
     </row>
     <row r="8" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="81">

--- a/dataland-framework-toolbox/inputs/eu-taxonomy-financials/eu-taxonomy-financials.xlsx
+++ b/dataland-framework-toolbox/inputs/eu-taxonomy-financials/eu-taxonomy-financials.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="721">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -2177,6 +2177,45 @@
   </si>
   <si>
     <t>Identity: [extendedCurrencyCreditInstitutionTurnoverBasedAssetsForCalculationOfGreenAssetRatioTurnoverBasedTotalGrossCarryingAmount]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount,extendedDecimalCreditInstitutionTurnoverBasedGreenAssetRatioStockSubstantialContributionToAnyOfTheSixEnvironmentalObjectivesInPercentEligible]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount,extendedDecimalCreditInstitutionTurnoverBasedGreenAssetRatioStockSubstantialContributionToAnyOfTheSixEnvironmentalObjectivesInPercentAligned]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount,extendedDecimalCreditInstitutionTurnoverBasedGreenAssetRatioStockSubstantialContributionToAnyOfTheSixEnvironmentalObjectivesInPercentOfWhichUseOfProceeds]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount,extendedDecimalCreditInstitutionTurnoverBasedGreenAssetRatioStockSubstantialContributionToAnyOfTheSixEnvironmentalObjectivesInPercentOfWhichTransitional]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount,extendedDecimalCreditInstitutionTurnoverBasedGreenAssetRatioStockSubstantialContributionToAnyOfTheSixEnvironmentalObjectivesInPercentOfWhichEnabling]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyAssetManagementAssetUnderManagementAssetsCoveredByTheKpiMonetaryAmount,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiTurnoverBasedShareOfTurnoverBasedKpiInPercentAligned]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyAssetManagementAssetUnderManagementAssetsCoveredByTheKpiMonetaryAmount,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiCapexBasedShareOfCapexBasedKpiInPercentAligned]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtraction: [extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyEligibleActivities,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyAlignedActivities]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtraction: [extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiums,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyEligibleActivities]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtraction: [extendedDecimalInsuranceReinsuranceProportionOfAbsolutePremiumsOfTaxonomyEligibleActivities,extendedDecimalInsuranceReinsuranceProportionOfAbsolutePremiumsOfTaxonomyAlignedActivities]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ComplementToPercent: [extendedDecimalInsuranceReinsuranceProportionOfAbsolutePremiumsOfTaxonomyEligibleActivities]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyInsuranceReinsuranceAssetUnderManagementAssetsCoveredByTheKpiMonetaryAmount,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiTurnoverBasedShareOfTurnoverBasedKpiInPercentAligned]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiplicationByPercent: [extendedCurrencyInsuranceReinsuranceAssetUnderManagementAssetsCoveredByTheKpiMonetaryAmount,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiCapexBasedShareOfCapexBasedKpiInPercentAligned]</t>
   </si>
 </sst>
 </file>
@@ -4054,6 +4093,9 @@
         <v>57</v>
       </c>
       <c r="P10" s="16"/>
+      <c r="Q10" s="16" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="53">
@@ -4094,6 +4136,9 @@
         <v>57</v>
       </c>
       <c r="P11" s="16"/>
+      <c r="Q11" s="16" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
@@ -4134,6 +4179,9 @@
         <v>57</v>
       </c>
       <c r="P12" s="24"/>
+      <c r="Q12" s="16" t="s">
+        <v>710</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
@@ -4174,6 +4222,9 @@
         <v>57</v>
       </c>
       <c r="P13" s="16"/>
+      <c r="Q13" s="16" t="s">
+        <v>711</v>
+      </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="82" t="s">
@@ -4214,6 +4265,9 @@
         <v>57</v>
       </c>
       <c r="P14" s="23"/>
+      <c r="Q14" s="16" t="s">
+        <v>712</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="25">
@@ -6686,6 +6740,9 @@
       </c>
       <c r="O79" s="16"/>
       <c r="P79" s="16"/>
+      <c r="Q79" s="16" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="80" spans="1:17" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="84">
@@ -6724,6 +6781,9 @@
       </c>
       <c r="O80" s="63"/>
       <c r="P80" s="63"/>
+      <c r="Q80" s="16" t="s">
+        <v>714</v>
+      </c>
     </row>
     <row r="81" spans="1:17" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A81" s="38">
@@ -7794,6 +7854,9 @@
       </c>
       <c r="O108" s="44"/>
       <c r="P108" s="44"/>
+      <c r="Q108" s="16" t="s">
+        <v>715</v>
+      </c>
     </row>
     <row r="109" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="43">
@@ -7832,6 +7895,9 @@
       </c>
       <c r="O109" s="44"/>
       <c r="P109" s="44"/>
+      <c r="Q109" s="16" t="s">
+        <v>716</v>
+      </c>
     </row>
     <row r="110" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="43">
@@ -7904,6 +7970,9 @@
       </c>
       <c r="O111" s="44"/>
       <c r="P111" s="44"/>
+      <c r="Q111" s="16" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="112" spans="1:16" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="34">
@@ -7940,6 +8009,9 @@
       </c>
       <c r="O112" s="59"/>
       <c r="P112" s="59"/>
+      <c r="Q112" s="16" t="s">
+        <v>718</v>
+      </c>
     </row>
     <row r="113" spans="1:17" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A113" s="43">
@@ -8056,6 +8128,9 @@
       </c>
       <c r="O115" s="16"/>
       <c r="P115" s="16"/>
+      <c r="Q115" s="16" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="116" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="34">
@@ -8094,6 +8169,9 @@
       </c>
       <c r="O116" s="63"/>
       <c r="P116" s="63"/>
+      <c r="Q116" s="16" t="s">
+        <v>720</v>
+      </c>
     </row>
     <row r="117" spans="1:17" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A117" s="43">
